--- a/artfynd/A 56895-2025 artfynd.xlsx
+++ b/artfynd/A 56895-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540324</v>
       </c>
       <c r="B2" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546235</v>
       </c>
       <c r="B3" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546591</v>
       </c>
       <c r="B4" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136542041</v>
       </c>
       <c r="B5" t="n">
-        <v>100955</v>
+        <v>100958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136544035</v>
       </c>
       <c r="B6" t="n">
-        <v>100955</v>
+        <v>100958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136542088</v>
       </c>
       <c r="B7" t="n">
-        <v>99651</v>
+        <v>99654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136550317</v>
       </c>
       <c r="B8" t="n">
-        <v>103025</v>
+        <v>103028</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56895-2025 artfynd.xlsx
+++ b/artfynd/A 56895-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540324</v>
       </c>
       <c r="B2" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546235</v>
       </c>
       <c r="B3" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546591</v>
       </c>
       <c r="B4" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136542041</v>
       </c>
       <c r="B5" t="n">
-        <v>100958</v>
+        <v>100959</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136544035</v>
       </c>
       <c r="B6" t="n">
-        <v>100958</v>
+        <v>100959</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136542088</v>
       </c>
       <c r="B7" t="n">
-        <v>99654</v>
+        <v>99655</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136550317</v>
       </c>
       <c r="B8" t="n">
-        <v>103028</v>
+        <v>103029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56895-2025 artfynd.xlsx
+++ b/artfynd/A 56895-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540324</v>
       </c>
       <c r="B2" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546235</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546591</v>
       </c>
       <c r="B4" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136542041</v>
       </c>
       <c r="B5" t="n">
-        <v>100959</v>
+        <v>100964</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136544035</v>
       </c>
       <c r="B6" t="n">
-        <v>100959</v>
+        <v>100964</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136542088</v>
       </c>
       <c r="B7" t="n">
-        <v>99655</v>
+        <v>99660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136550317</v>
       </c>
       <c r="B8" t="n">
-        <v>103029</v>
+        <v>103034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56895-2025 artfynd.xlsx
+++ b/artfynd/A 56895-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540324</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546235</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546591</v>
       </c>
       <c r="B4" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136542041</v>
       </c>
       <c r="B5" t="n">
-        <v>100964</v>
+        <v>100966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136544035</v>
       </c>
       <c r="B6" t="n">
-        <v>100964</v>
+        <v>100966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136542088</v>
       </c>
       <c r="B7" t="n">
-        <v>99660</v>
+        <v>99662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136550317</v>
       </c>
       <c r="B8" t="n">
-        <v>103034</v>
+        <v>103036</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56895-2025 artfynd.xlsx
+++ b/artfynd/A 56895-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540324</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546235</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546591</v>
       </c>
       <c r="B4" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136542041</v>
       </c>
       <c r="B5" t="n">
-        <v>100966</v>
+        <v>100972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136544035</v>
       </c>
       <c r="B6" t="n">
-        <v>100966</v>
+        <v>100972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136542088</v>
       </c>
       <c r="B7" t="n">
-        <v>99662</v>
+        <v>99668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136550317</v>
       </c>
       <c r="B8" t="n">
-        <v>103036</v>
+        <v>103042</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56895-2025 artfynd.xlsx
+++ b/artfynd/A 56895-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540324</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546235</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546591</v>
       </c>
       <c r="B4" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136542041</v>
       </c>
       <c r="B5" t="n">
-        <v>100972</v>
+        <v>100974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136544035</v>
       </c>
       <c r="B6" t="n">
-        <v>100972</v>
+        <v>100974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136542088</v>
       </c>
       <c r="B7" t="n">
-        <v>99668</v>
+        <v>99670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136550317</v>
       </c>
       <c r="B8" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56895-2025 artfynd.xlsx
+++ b/artfynd/A 56895-2025 artfynd.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Johanna Björkman</t>
+          <t>Johanna Björkman, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 56895-2025 artfynd.xlsx
+++ b/artfynd/A 56895-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540324</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546235</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546591</v>
       </c>
       <c r="B4" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136542041</v>
       </c>
       <c r="B5" t="n">
-        <v>100974</v>
+        <v>100975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136544035</v>
       </c>
       <c r="B6" t="n">
-        <v>100974</v>
+        <v>100975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johanna Björkman, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>136542088</v>
       </c>
       <c r="B7" t="n">
-        <v>99670</v>
+        <v>99671</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136550317</v>
       </c>
       <c r="B8" t="n">
-        <v>103044</v>
+        <v>103045</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56895-2025 artfynd.xlsx
+++ b/artfynd/A 56895-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540324</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546235</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546591</v>
       </c>
       <c r="B4" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136542041</v>
       </c>
       <c r="B5" t="n">
-        <v>100975</v>
+        <v>100981</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136544035</v>
       </c>
       <c r="B6" t="n">
-        <v>100975</v>
+        <v>100981</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136542088</v>
       </c>
       <c r="B7" t="n">
-        <v>99671</v>
+        <v>99677</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136550317</v>
       </c>
       <c r="B8" t="n">
-        <v>103045</v>
+        <v>103051</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56895-2025 artfynd.xlsx
+++ b/artfynd/A 56895-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540324</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546235</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546591</v>
       </c>
       <c r="B4" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136542041</v>
       </c>
       <c r="B5" t="n">
-        <v>100981</v>
+        <v>100985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136544035</v>
       </c>
       <c r="B6" t="n">
-        <v>100981</v>
+        <v>100985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136542088</v>
       </c>
       <c r="B7" t="n">
-        <v>99677</v>
+        <v>99681</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136550317</v>
       </c>
       <c r="B8" t="n">
-        <v>103051</v>
+        <v>103055</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56895-2025 artfynd.xlsx
+++ b/artfynd/A 56895-2025 artfynd.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 56895-2025 artfynd.xlsx
+++ b/artfynd/A 56895-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540324</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546235</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -895,7 +895,7 @@
         <v>136546591</v>
       </c>
       <c r="B4" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136542041</v>
       </c>
       <c r="B5" t="n">
-        <v>100985</v>
+        <v>100987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1107,7 +1107,7 @@
         <v>136544035</v>
       </c>
       <c r="B6" t="n">
-        <v>100985</v>
+        <v>100987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136542088</v>
       </c>
       <c r="B7" t="n">
-        <v>99681</v>
+        <v>99683</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136550317</v>
       </c>
       <c r="B8" t="n">
-        <v>103055</v>
+        <v>103057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56895-2025 artfynd.xlsx
+++ b/artfynd/A 56895-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540324</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546235</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546591</v>
       </c>
       <c r="B4" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136542041</v>
       </c>
       <c r="B5" t="n">
-        <v>100987</v>
+        <v>100989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136544035</v>
       </c>
       <c r="B6" t="n">
-        <v>100987</v>
+        <v>100989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Johanna Björkman</t>
+          <t>Johanna Björkman, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>136542088</v>
       </c>
       <c r="B7" t="n">
-        <v>99683</v>
+        <v>99685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136550317</v>
       </c>
       <c r="B8" t="n">
-        <v>103057</v>
+        <v>103059</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56895-2025 artfynd.xlsx
+++ b/artfynd/A 56895-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540324</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546235</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546591</v>
       </c>
       <c r="B4" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136542041</v>
       </c>
       <c r="B5" t="n">
-        <v>100989</v>
+        <v>101002</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136544035</v>
       </c>
       <c r="B6" t="n">
-        <v>100989</v>
+        <v>101002</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johanna Björkman, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>136542088</v>
       </c>
       <c r="B7" t="n">
-        <v>99685</v>
+        <v>99698</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136550317</v>
       </c>
       <c r="B8" t="n">
-        <v>103059</v>
+        <v>103072</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56895-2025 artfynd.xlsx
+++ b/artfynd/A 56895-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540324</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136546235</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546591</v>
       </c>
       <c r="B4" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136542041</v>
       </c>
       <c r="B5" t="n">
-        <v>101002</v>
+        <v>101004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136544035</v>
       </c>
       <c r="B6" t="n">
-        <v>101002</v>
+        <v>101004</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136542088</v>
       </c>
       <c r="B7" t="n">
-        <v>99698</v>
+        <v>99700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136550317</v>
       </c>
       <c r="B8" t="n">
-        <v>103072</v>
+        <v>103074</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
